--- a/Locatoin_prediction_usingRSS_signal/Book1.xlsx
+++ b/Locatoin_prediction_usingRSS_signal/Book1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Machine LearningHarry\IITPatna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmd04\OneDrive\Documents\GitHub\Data-Analyst\Locatoin_prediction_usingRSS_signal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DB67CEB-0858-425D-A266-6B2125E233A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FAD2AD-AFC0-4228-A46E-6B66FDA6717C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E399460-D69A-49F1-A772-65A69D6857E2}"/>
   </bookViews>
@@ -84,16 +84,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA492DBF-86D0-4379-9B44-0C65B77DF0A3}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -428,24 +426,24 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>2.17640881067986</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>0.46995988439051301</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>2.1247051168974398</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>0.46995988439051301</v>
       </c>
     </row>
@@ -456,7 +454,7 @@
       <c r="B4">
         <v>2.37988512778101</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>0.46995988439051301</v>
       </c>
     </row>
@@ -489,7 +487,7 @@
       <c r="B7">
         <v>2.3178455658481698</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <v>0.46995988439051301</v>
       </c>
     </row>
@@ -700,6 +698,16 @@
       </c>
       <c r="C26">
         <v>0.46995988439051301</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <f>SUM(B2:B26)/25</f>
+        <v>3.5384600625471045</v>
+      </c>
+      <c r="C27">
+        <f>SUM(C2:C26)/25</f>
+        <v>0.46995988439051273</v>
       </c>
     </row>
   </sheetData>
